--- a/input-rsp/RSP_Outbound_May26.xlsx
+++ b/input-rsp/RSP_Outbound_May26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ9"/>
+  <dimension ref="A1:DQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,21 +1116,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2120001</t>
+          <t>901OBMay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -1139,39 +1139,43 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>สมชาย</t>
+          <t>Piti</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ใจดี</t>
+          <t>Cross</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2120000000212</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr"/>
+          <t>2020000000901</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Self-Employed</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2120002</t>
+          <t>902OBMay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18000</v>
+        <v>100000</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1180,39 +1184,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>สมหญิง</t>
+          <t>Somchai</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ใจทรนง</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2120000000213</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr"/>
+          <t>2020000000902</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Self-Employed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1010001</t>
+          <t>2120001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1221,17 +1229,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>SOMSAK</t>
+          <t>สมชาย</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>SANCTION</t>
+          <t>ใจดี</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1100000000101</t>
+          <t>2120000000212</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr"/>
@@ -1239,21 +1247,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1010002</t>
+          <t>2120002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>09:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,17 +1270,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>NARONG</t>
+          <t>สมหญิง</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>CRIMINAL</t>
+          <t>ใจทรนง</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1100000000202</t>
+          <t>2120000000213</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr"/>
@@ -1280,21 +1288,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1010003</t>
+          <t>1010001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10:10:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60000</v>
+        <v>25000</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1303,17 +1311,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>SOMSAK</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>PETROV</t>
+          <t>SANCTION</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>UN0001234</t>
+          <t>1100000000101</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr"/>
@@ -1321,43 +1329,125 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>1010002</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>09:45:00</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>40000</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ATH160001</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>NARONG</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>CRIMINAL</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>1100000000202</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1010003</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10:10:00</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>60000</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ATH160001</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>IVAN</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>PETROV</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>UN0001234</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>1010004</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>15000</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>ATH160001</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>UN0009999</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
